--- a/benchmark_month_end.xlsx
+++ b/benchmark_month_end.xlsx
@@ -5151,19 +5151,19 @@
         </is>
       </c>
       <c r="B214" s="3" t="n">
-        <v>-0.272698</v>
+        <v>-0.21713</v>
       </c>
       <c r="C214" s="3" t="n">
-        <v>-0.311064</v>
+        <v>-0.238952</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>-0.280634</v>
+        <v>-0.187086</v>
       </c>
       <c r="E214" s="3" t="n">
-        <v>-0.702322</v>
+        <v>-0.243903</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>0.680616</v>
+        <v>2.027801</v>
       </c>
     </row>
     <row r="215">
@@ -5177,7 +5177,7 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>As of 2026-09-01 — every series ends on this same trading day. Monthly total return in PERCENT, months keyed YYYY-MM. For the tracker's Power Query feed use benchmark_month_end_combined.csv instead: same returns as DECIMALS, keyed on the last calendar day of each month, complete months only. Total return with distributions reinvested on the ex-date at the ex-date close, i.e. a day's return is (C[t] + D) / C[t-1]. Reconstructed from the raw (unadjusted) close plus the distribution history corrected by benchmarks/distribution_overrides.csv. ^SP500TR and ^TA125.TA are index levels, passed through without reconstruction. PASTE SOURCE FOR THE TRACKER: the Combined sheet (monthly returns). Adjusted closes are for audit only — never paste price levels into the tracker.</t>
+          <t>As of 2026-09-02 — every series ends on this same trading day. Monthly total return in PERCENT, months keyed YYYY-MM. For the tracker's Power Query feed use benchmark_month_end_combined.csv instead: same returns as DECIMALS, keyed on the last calendar day of each month, complete months only. Total return with distributions reinvested on the ex-date at the ex-date close, i.e. a day's return is (C[t] + D) / C[t-1]. Reconstructed from the raw (unadjusted) close plus the distribution history corrected by benchmarks/distribution_overrides.csv. ^SP500TR and ^TA125.TA are index levels, passed through without reconstruction. PASTE SOURCE FOR THE TRACKER: the Combined sheet (monthly returns). Adjusted closes are for audit only — never paste price levels into the tracker.</t>
         </is>
       </c>
     </row>
@@ -9687,17 +9687,17 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
-        <v>71.790001</v>
+        <v>71.83000199999999</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>71.790001</v>
+        <v>71.83000199999999</v>
       </c>
       <c r="E214" s="3" t="n">
-        <v>-0.272698</v>
+        <v>-0.21713</v>
       </c>
     </row>
     <row r="215">
@@ -9710,7 +9710,7 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>BND (reconstructed TR) (BND, ETF) · as of 2026-09-01. Total return with distributions reinvested on the ex-date at the ex-date close, i.e. a day's return is (C[t] + D) / C[t-1]. Reconstructed from the raw (unadjusted) close plus the distribution history corrected by benchmarks/distribution_overrides.csv. ^SP500TR and ^TA125.TA are index levels, passed through without reconstruction. PASTE SOURCE FOR THE TRACKER: the Combined sheet (monthly returns). Adjusted closes are for audit only — never paste price levels into the tracker.</t>
+          <t>BND (reconstructed TR) (BND, ETF) · as of 2026-09-02. Total return with distributions reinvested on the ex-date at the ex-date close, i.e. a day's return is (C[t] + D) / C[t-1]. Reconstructed from the raw (unadjusted) close plus the distribution history corrected by benchmarks/distribution_overrides.csv. ^SP500TR and ^TA125.TA are index levels, passed through without reconstruction. PASTE SOURCE FOR THE TRACKER: the Combined sheet (monthly returns). Adjusted closes are for audit only — never paste price levels into the tracker.</t>
         </is>
       </c>
     </row>
@@ -14220,17 +14220,17 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
-        <v>96.769997</v>
+        <v>96.839996</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>96.769997</v>
+        <v>96.839996</v>
       </c>
       <c r="E214" s="3" t="n">
-        <v>-0.311064</v>
+        <v>-0.238952</v>
       </c>
     </row>
     <row r="215">
@@ -14243,7 +14243,7 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>AGG (reconstructed TR) (AGG, ETF) · as of 2026-09-01. Total return with distributions reinvested on the ex-date at the ex-date close, i.e. a day's return is (C[t] + D) / C[t-1]. Reconstructed from the raw (unadjusted) close plus the distribution history corrected by benchmarks/distribution_overrides.csv. ^SP500TR and ^TA125.TA are index levels, passed through without reconstruction. PASTE SOURCE FOR THE TRACKER: the Combined sheet (monthly returns). Adjusted closes are for audit only — never paste price levels into the tracker.</t>
+          <t>AGG (reconstructed TR) (AGG, ETF) · as of 2026-09-02. Total return with distributions reinvested on the ex-date at the ex-date close, i.e. a day's return is (C[t] + D) / C[t-1]. Reconstructed from the raw (unadjusted) close plus the distribution history corrected by benchmarks/distribution_overrides.csv. ^SP500TR and ^TA125.TA are index levels, passed through without reconstruction. PASTE SOURCE FOR THE TRACKER: the Combined sheet (monthly returns). Adjusted closes are for audit only — never paste price levels into the tracker.</t>
         </is>
       </c>
     </row>
@@ -18753,17 +18753,17 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
-        <v>10.66</v>
+        <v>10.67</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>10.66</v>
+        <v>10.67</v>
       </c>
       <c r="E214" s="3" t="n">
-        <v>-0.280634</v>
+        <v>-0.187086</v>
       </c>
     </row>
     <row r="215">
@@ -18776,7 +18776,7 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>PIMIX (reconstructed TR) (PIMIX, Mutual fund) · as of 2026-09-01. Total return with distributions reinvested on the ex-date at the ex-date close, i.e. a day's return is (C[t] + D) / C[t-1]. Reconstructed from the raw (unadjusted) close plus the distribution history corrected by benchmarks/distribution_overrides.csv. ^SP500TR and ^TA125.TA are index levels, passed through without reconstruction. PASTE SOURCE FOR THE TRACKER: the Combined sheet (monthly returns). Adjusted closes are for audit only — never paste price levels into the tracker.</t>
+          <t>PIMIX (reconstructed TR) (PIMIX, Mutual fund) · as of 2026-09-02. Total return with distributions reinvested on the ex-date at the ex-date close, i.e. a day's return is (C[t] + D) / C[t-1]. Reconstructed from the raw (unadjusted) close plus the distribution history corrected by benchmarks/distribution_overrides.csv. ^SP500TR and ^TA125.TA are index levels, passed through without reconstruction. PASTE SOURCE FOR THE TRACKER: the Combined sheet (monthly returns). Adjusted closes are for audit only — never paste price levels into the tracker.</t>
         </is>
       </c>
     </row>
@@ -22516,7 +22516,7 @@
         <v>9709.679688</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>9709.679688</v>
+        <v>9709.679687</v>
       </c>
       <c r="E177" s="3" t="n">
         <v>-1.59211</v>
@@ -23286,17 +23286,17 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
-        <v>17099</v>
+        <v>17177.939453</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>17099</v>
+        <v>17177.939453</v>
       </c>
       <c r="E214" s="3" t="n">
-        <v>-0.702322</v>
+        <v>-0.243903</v>
       </c>
     </row>
     <row r="215">
@@ -23309,7 +23309,7 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>S&amp;P 500 total return (^SP500TR, TR index) · as of 2026-09-01. Total return with distributions reinvested on the ex-date at the ex-date close, i.e. a day's return is (C[t] + D) / C[t-1]. Reconstructed from the raw (unadjusted) close plus the distribution history corrected by benchmarks/distribution_overrides.csv. ^SP500TR and ^TA125.TA are index levels, passed through without reconstruction. PASTE SOURCE FOR THE TRACKER: the Combined sheet (monthly returns). Adjusted closes are for audit only — never paste price levels into the tracker.</t>
+          <t>S&amp;P 500 total return (^SP500TR, TR index) · as of 2026-09-02. Total return with distributions reinvested on the ex-date at the ex-date close, i.e. a day's return is (C[t] + D) / C[t-1]. Reconstructed from the raw (unadjusted) close plus the distribution history corrected by benchmarks/distribution_overrides.csv. ^SP500TR and ^TA125.TA are index levels, passed through without reconstruction. PASTE SOURCE FOR THE TRACKER: the Combined sheet (monthly returns). Adjusted closes are for audit only — never paste price levels into the tracker.</t>
         </is>
       </c>
     </row>
@@ -27819,17 +27819,17 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
-        <v>4084.209961</v>
+        <v>4138.859863</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>4084.209961</v>
+        <v>4138.859863</v>
       </c>
       <c r="E214" s="3" t="n">
-        <v>0.680616</v>
+        <v>2.027801</v>
       </c>
     </row>
     <row r="215">
@@ -27842,7 +27842,7 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>TA-125 (^TA125.TA, Index) · as of 2026-09-01. Total return with distributions reinvested on the ex-date at the ex-date close, i.e. a day's return is (C[t] + D) / C[t-1]. Reconstructed from the raw (unadjusted) close plus the distribution history corrected by benchmarks/distribution_overrides.csv. ^SP500TR and ^TA125.TA are index levels, passed through without reconstruction. PASTE SOURCE FOR THE TRACKER: the Combined sheet (monthly returns). Adjusted closes are for audit only — never paste price levels into the tracker.</t>
+          <t>TA-125 (^TA125.TA, Index) · as of 2026-09-02. Total return with distributions reinvested on the ex-date at the ex-date close, i.e. a day's return is (C[t] + D) / C[t-1]. Reconstructed from the raw (unadjusted) close plus the distribution history corrected by benchmarks/distribution_overrides.csv. ^SP500TR and ^TA125.TA are index levels, passed through without reconstruction. PASTE SOURCE FOR THE TRACKER: the Combined sheet (monthly returns). Adjusted closes are for audit only — never paste price levels into the tracker.</t>
         </is>
       </c>
     </row>
